--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9021,0.0029,0.0079,0.0843</t>
-  </si>
-  <si>
-    <t>0.0026,0.0060,0.0004,0.9986</t>
-  </si>
-  <si>
-    <t>0.8601,0.0463,0.0187,0.0522</t>
-  </si>
-  <si>
-    <t>0.5531,0.0037,0.0123,0.5641</t>
-  </si>
-  <si>
-    <t>0.9976,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0026,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9747,0.0248,0.0049,0.0009</t>
-  </si>
-  <si>
-    <t>0.9952,0.0038,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9916,0.0077,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9967,0.0020,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9937,0.0030,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0016,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.4062,0.6202,0.0534,0.0116</t>
-  </si>
-  <si>
-    <t>0.5064,0.0918,0.5109,0.0049</t>
-  </si>
-  <si>
-    <t>0.2145,0.0607,0.7483,0.0014</t>
-  </si>
-  <si>
-    <t>0.1274,0.0566,0.8338,0.0113</t>
-  </si>
-  <si>
-    <t>0.5824,0.1557,0.3454,0.0165</t>
-  </si>
-  <si>
-    <t>0.0264,0.9647,0.0092,0.0011</t>
-  </si>
-  <si>
-    <t>0.0608,0.9470,0.0055,0.0008</t>
-  </si>
-  <si>
-    <t>0.6200,0.4346,0.0327,0.0030</t>
-  </si>
-  <si>
-    <t>0.0603,0.9465,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.0832,0.9386,0.0055,0.0004</t>
-  </si>
-  <si>
-    <t>0.3039,0.0083,0.7011,0.0478</t>
-  </si>
-  <si>
-    <t>0.4365,0.0099,0.7416,0.0060</t>
-  </si>
-  <si>
-    <t>0.0545,0.0090,0.9550,0.0033</t>
-  </si>
-  <si>
-    <t>0.1636,0.0087,0.8845,0.0045</t>
-  </si>
-  <si>
-    <t>0.0843,0.0072,0.9356,0.0104</t>
-  </si>
-  <si>
-    <t>0.5909,0.0042,0.6087,0.0056</t>
-  </si>
-  <si>
-    <t>0.0093,0.0047,0.9832,0.0054</t>
-  </si>
-  <si>
-    <t>0.1725,0.8889,0.0035,0.0009</t>
-  </si>
-  <si>
-    <t>0.4557,0.2321,0.4227,0.0128</t>
-  </si>
-  <si>
-    <t>0.0030,0.0299,0.9863,0.0021</t>
-  </si>
-  <si>
-    <t>0.0380,0.8504,0.1669,0.0003</t>
-  </si>
-  <si>
-    <t>0.4222,0.5730,0.0629,0.0118</t>
-  </si>
-  <si>
-    <t>0.3176,0.1764,0.5623,0.0051</t>
-  </si>
-  <si>
-    <t>0.4057,0.7307,0.0065,0.0014</t>
-  </si>
-  <si>
-    <t>0.1628,0.8746,0.0291,0.0019</t>
-  </si>
-  <si>
-    <t>0.0134,0.6748,0.1929,0.1756</t>
-  </si>
-  <si>
-    <t>0.0232,0.0119,0.9073,0.0894</t>
-  </si>
-  <si>
-    <t>0.0813,0.2670,0.7030,0.0729</t>
-  </si>
-  <si>
-    <t>0.1564,0.0048,0.8520,0.0224</t>
-  </si>
-  <si>
-    <t>0.1263,0.0815,0.8070,0.0060</t>
-  </si>
-  <si>
-    <t>0.0015,0.9925,0.0066,0.0001</t>
-  </si>
-  <si>
-    <t>0.0097,0.2178,0.9482,0.0092</t>
-  </si>
-  <si>
-    <t>0.0744,0.8051,0.0125,0.2907</t>
-  </si>
-  <si>
-    <t>0.0041,0.9756,0.0110,0.0240</t>
-  </si>
-  <si>
-    <t>0.0132,0.9259,0.1931,0.0019</t>
-  </si>
-  <si>
-    <t>0.0077,0.9777,0.0256,0.0037</t>
-  </si>
-  <si>
-    <t>0.0027,0.0315,0.9848,0.0031</t>
-  </si>
-  <si>
-    <t>0.0020,0.0859,0.9920,0.0002</t>
-  </si>
-  <si>
-    <t>0.0797,0.0301,0.8892,0.0076</t>
-  </si>
-  <si>
-    <t>0.0388,0.0089,0.9524,0.0079</t>
-  </si>
-  <si>
-    <t>0.0096,0.0115,0.9729,0.0154</t>
-  </si>
-  <si>
-    <t>0.0024,0.0088,0.9901,0.0013</t>
-  </si>
-  <si>
-    <t>0.9218,0.1082,0.0055,0.0015</t>
-  </si>
-  <si>
-    <t>0.9655,0.0301,0.0100,0.0007</t>
-  </si>
-  <si>
-    <t>0.9063,0.1055,0.0233,0.0033</t>
-  </si>
-  <si>
-    <t>0.0059,0.0634,0.9798,0.0020</t>
-  </si>
-  <si>
-    <t>0.9897,0.0100,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0013,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9771,0.0183,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.0025,0.9048,0.8798,0.0004</t>
-  </si>
-  <si>
-    <t>0.0240,0.0521,0.9675,0.0027</t>
-  </si>
-  <si>
-    <t>0.0093,0.0208,0.9410,0.0591</t>
-  </si>
-  <si>
-    <t>0.0002,0.9175,0.9797,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0014,0.9972,0.0019</t>
-  </si>
-  <si>
-    <t>0.0712,0.9034,0.0696,0.0013</t>
-  </si>
-  <si>
-    <t>0.0110,0.9881,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.8389,0.0094,0.2518,0.0030</t>
-  </si>
-  <si>
-    <t>0.4619,0.1307,0.4463,0.0028</t>
-  </si>
-  <si>
-    <t>0.0118,0.1310,0.9668,0.0016</t>
-  </si>
-  <si>
-    <t>0.0011,0.9656,0.6364,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.8104,0.8701,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.9820,0.2355,0.0033</t>
-  </si>
-  <si>
-    <t>0.0007,0.9384,0.8878,0.0000</t>
-  </si>
-  <si>
-    <t>0.0497,0.0004,0.0155,0.9614</t>
-  </si>
-  <si>
-    <t>0.0029,0.0080,0.0011,0.9979</t>
-  </si>
-  <si>
-    <t>0.0093,0.0037,0.0008,0.9958</t>
-  </si>
-  <si>
-    <t>0.0257,0.0117,0.0049,0.9828</t>
-  </si>
-  <si>
-    <t>0.0271,0.0030,0.0031,0.9880</t>
-  </si>
-  <si>
-    <t>0.0086,0.0015,0.0054,0.9926</t>
-  </si>
-  <si>
-    <t>0.0010,0.9737,0.6336,0.0006</t>
-  </si>
-  <si>
-    <t>0.0019,0.5173,0.9650,0.0004</t>
-  </si>
-  <si>
-    <t>0.0290,0.6219,0.6818,0.0120</t>
-  </si>
-  <si>
-    <t>0.0154,0.6450,0.6894,0.0046</t>
-  </si>
-  <si>
-    <t>0.0013,0.9503,0.6804,0.0001</t>
-  </si>
-  <si>
-    <t>0.0043,0.7318,0.7683,0.0006</t>
-  </si>
-  <si>
-    <t>0.9920,0.0101,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9904,0.0105,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9543,0.0563,0.0063,0.0013</t>
-  </si>
-  <si>
-    <t>0.9918,0.0019,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9912,0.0070,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9958,0.0032,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9902,0.0186,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9908,0.0077,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9964,0.0028,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0023,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9958,0.0015,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9849,0.0087,0.0024,0.0013</t>
-  </si>
-  <si>
-    <t>0.9928,0.0090,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9943,0.0030,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9938,0.0032,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.0054,0.0029,0.9835,0.0195</t>
-  </si>
-  <si>
-    <t>0.0236,0.0156,0.9589,0.0007</t>
-  </si>
-  <si>
-    <t>0.7921,0.0262,0.0417,0.0794</t>
-  </si>
-  <si>
-    <t>0.0819,0.0080,0.9300,0.0036</t>
-  </si>
-  <si>
-    <t>0.0818,0.9307,0.0068,0.0005</t>
-  </si>
-  <si>
-    <t>0.0579,0.9469,0.0052,0.0007</t>
-  </si>
-  <si>
-    <t>0.0601,0.9365,0.0003,0.0016</t>
-  </si>
-  <si>
-    <t>0.3964,0.7053,0.0096,0.0011</t>
-  </si>
-  <si>
-    <t>0.0644,0.9340,0.0030,0.0018</t>
-  </si>
-  <si>
-    <t>0.0147,0.9818,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.3698,0.7588,0.0079,0.0005</t>
-  </si>
-  <si>
-    <t>0.4635,0.0933,0.5504,0.0196</t>
-  </si>
-  <si>
-    <t>0.3186,0.0621,0.6930,0.0093</t>
-  </si>
-  <si>
-    <t>0.1886,0.4089,0.3496,0.0202</t>
-  </si>
-  <si>
-    <t>0.5744,0.0763,0.4395,0.0115</t>
-  </si>
-  <si>
-    <t>0.0408,0.7040,0.0144,0.6081</t>
-  </si>
-  <si>
-    <t>0.0252,0.9340,0.2101,0.0048</t>
-  </si>
-  <si>
-    <t>0.0031,0.9833,0.0112,0.0085</t>
-  </si>
-  <si>
-    <t>0.0442,0.9120,0.0515,0.0079</t>
-  </si>
-  <si>
-    <t>0.0054,0.9437,0.6795,0.0016</t>
-  </si>
-  <si>
-    <t>0.1058,0.9257,0.0196,0.0002</t>
-  </si>
-  <si>
-    <t>0.7989,0.2055,0.0278,0.0007</t>
-  </si>
-  <si>
-    <t>0.2785,0.7396,0.0268,0.0005</t>
-  </si>
-  <si>
-    <t>0.9775,0.0315,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9613,0.0136,0.0047,0.0065</t>
-  </si>
-  <si>
-    <t>0.9888,0.0035,0.0003,0.0019</t>
-  </si>
-  <si>
-    <t>0.9737,0.0109,0.0040,0.0036</t>
-  </si>
-  <si>
-    <t>0.9916,0.0047,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9728,0.0142,0.0143,0.0014</t>
-  </si>
-  <si>
-    <t>0.9905,0.0038,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9721,0.0164,0.0063,0.0025</t>
-  </si>
-  <si>
-    <t>0.0170,0.6455,0.7475,0.0045</t>
-  </si>
-  <si>
-    <t>0.0020,0.8607,0.8728,0.0002</t>
-  </si>
-  <si>
-    <t>0.0278,0.2351,0.8473,0.0008</t>
-  </si>
-  <si>
-    <t>0.0900,0.3119,0.6417,0.0644</t>
-  </si>
-  <si>
-    <t>0.6658,0.2795,0.0370,0.0358</t>
-  </si>
-  <si>
-    <t>0.4083,0.3599,0.2932,0.0436</t>
-  </si>
-  <si>
-    <t>0.2397,0.0028,0.8957,0.0059</t>
-  </si>
-  <si>
-    <t>0.3298,0.4097,0.2761,0.0251</t>
-  </si>
-  <si>
-    <t>0.1232,0.0039,0.0054,0.9478</t>
-  </si>
-  <si>
-    <t>0.0001,0.0029,0.0017,0.9996</t>
-  </si>
-  <si>
-    <t>0.0086,0.0102,0.0028,0.9938</t>
-  </si>
-  <si>
-    <t>0.0630,0.0002,0.0146,0.9469</t>
-  </si>
-  <si>
-    <t>0.0039,0.8908,0.7790,0.0010</t>
-  </si>
-  <si>
-    <t>0.9323,0.0755,0.0082,0.0012</t>
-  </si>
-  <si>
-    <t>0.1207,0.8909,0.0030,0.0049</t>
-  </si>
-  <si>
-    <t>0.9800,0.0117,0.0012,0.0020</t>
-  </si>
-  <si>
-    <t>0.6780,0.4461,0.0081,0.0017</t>
-  </si>
-  <si>
-    <t>0.9840,0.0054,0.0026,0.0018</t>
-  </si>
-  <si>
-    <t>0.8716,0.0023,0.0138,0.1026</t>
-  </si>
-  <si>
-    <t>0.9708,0.0010,0.0004,0.0298</t>
-  </si>
-  <si>
-    <t>0.0074,0.1707,0.9384,0.0246</t>
-  </si>
-  <si>
-    <t>0.9037,0.0022,0.0518,0.0243</t>
-  </si>
-  <si>
-    <t>0.9173,0.0077,0.0060,0.0473</t>
-  </si>
-  <si>
-    <t>0.1117,0.8997,0.0061,0.0036</t>
-  </si>
-  <si>
-    <t>0.6348,0.3416,0.0763,0.0217</t>
-  </si>
-  <si>
-    <t>0.8513,0.0839,0.1025,0.0041</t>
-  </si>
-  <si>
-    <t>0.5094,0.5373,0.0262,0.0048</t>
-  </si>
-  <si>
-    <t>0.7201,0.2867,0.0461,0.0017</t>
-  </si>
-  <si>
-    <t>0.7609,0.2791,0.0230,0.0045</t>
-  </si>
-  <si>
-    <t>0.9908,0.0045,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9728,0.0165,0.0018,0.0029</t>
-  </si>
-  <si>
-    <t>0.9953,0.0025,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9947,0.0010,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9904,0.0045,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9902,0.0023,0.0002,0.0017</t>
-  </si>
-  <si>
-    <t>0.9952,0.0007,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9894,0.0015,0.0011,0.0025</t>
-  </si>
-  <si>
-    <t>0.2004,0.8358,0.0021,0.0028</t>
-  </si>
-  <si>
-    <t>0.8773,0.1636,0.0154,0.0018</t>
-  </si>
-  <si>
-    <t>0.3535,0.7306,0.0189,0.0016</t>
-  </si>
-  <si>
-    <t>0.4432,0.2034,0.4421,0.0107</t>
-  </si>
-  <si>
-    <t>0.9677,0.0274,0.0020,0.0021</t>
-  </si>
-  <si>
-    <t>0.9388,0.0501,0.0117,0.0028</t>
-  </si>
-  <si>
-    <t>0.9850,0.0110,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9713,0.0125,0.0042,0.0032</t>
-  </si>
-  <si>
-    <t>0.0012,0.0381,0.9956,0.0003</t>
-  </si>
-  <si>
-    <t>0.9342,0.0683,0.0032,0.0036</t>
-  </si>
-  <si>
-    <t>0.0022,0.0186,0.9913,0.0005</t>
-  </si>
-  <si>
-    <t>0.0457,0.0784,0.9262,0.0079</t>
-  </si>
-  <si>
-    <t>0.0587,0.0066,0.9591,0.0015</t>
-  </si>
-  <si>
-    <t>0.0079,0.0568,0.9651,0.0036</t>
-  </si>
-  <si>
-    <t>0.0162,0.0186,0.9767,0.0014</t>
-  </si>
-  <si>
-    <t>0.0254,0.0019,0.9864,0.0007</t>
-  </si>
-  <si>
-    <t>0.0028,0.0018,0.9945,0.0008</t>
-  </si>
-  <si>
-    <t>0.2758,0.0366,0.7799,0.0254</t>
-  </si>
-  <si>
-    <t>0.4587,0.0821,0.5811,0.0103</t>
-  </si>
-  <si>
-    <t>0.4153,0.0459,0.6853,0.0111</t>
-  </si>
-  <si>
-    <t>0.1418,0.7191,0.2446,0.0077</t>
-  </si>
-  <si>
-    <t>0.0600,0.1620,0.7928,0.0050</t>
-  </si>
-  <si>
-    <t>0.3638,0.3624,0.2618,0.0163</t>
-  </si>
-  <si>
-    <t>0.5965,0.0706,0.4409,0.0130</t>
-  </si>
-  <si>
-    <t>0.3473,0.0247,0.7445,0.0160</t>
-  </si>
-  <si>
-    <t>0.9245,0.1190,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.8920,0.1343,0.0131,0.0004</t>
-  </si>
-  <si>
-    <t>0.6965,0.3924,0.0203,0.0008</t>
-  </si>
-  <si>
-    <t>0.9899,0.0112,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.7849,0.3884,0.0043,0.0009</t>
-  </si>
-  <si>
-    <t>0.6780,0.2131,0.1308,0.0091</t>
-  </si>
-  <si>
-    <t>0.7420,0.0438,0.3179,0.0090</t>
-  </si>
-  <si>
-    <t>0.6599,0.0840,0.0904,0.1936</t>
-  </si>
-  <si>
-    <t>0.5651,0.0664,0.0556,0.4385</t>
-  </si>
-  <si>
-    <t>0.7832,0.0043,0.2411,0.0208</t>
-  </si>
-  <si>
-    <t>0.0110,0.0101,0.9701,0.0126</t>
-  </si>
-  <si>
-    <t>0.0139,0.6955,0.8311,0.0052</t>
-  </si>
-  <si>
-    <t>0.0323,0.3088,0.7795,0.0044</t>
-  </si>
-  <si>
-    <t>0.0351,0.0970,0.8927,0.0043</t>
-  </si>
-  <si>
-    <t>0.0342,0.6307,0.4437,0.0087</t>
-  </si>
-  <si>
-    <t>0.9895,0.0008,0.0000,0.0031</t>
-  </si>
-  <si>
-    <t>0.9853,0.0149,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0011,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9959,0.0017,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9915,0.0059,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9848,0.0144,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.9882,0.0103,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9933,0.0035,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.1017,0.0202,0.9273,0.0021</t>
-  </si>
-  <si>
-    <t>0.1211,0.2229,0.7298,0.0054</t>
-  </si>
-  <si>
-    <t>0.7121,0.1957,0.1444,0.0217</t>
-  </si>
-  <si>
-    <t>0.0073,0.0312,0.9866,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0141,0.9955,0.0006</t>
-  </si>
-  <si>
-    <t>0.0259,0.1381,0.8712,0.0084</t>
-  </si>
-  <si>
-    <t>0.0011,0.0031,0.9932,0.0040</t>
-  </si>
-  <si>
-    <t>0.2771,0.0819,0.6434,0.0500</t>
-  </si>
-  <si>
-    <t>0.0036,0.0365,0.9742,0.0091</t>
-  </si>
-  <si>
-    <t>0.0607,0.1154,0.8167,0.0169</t>
-  </si>
-  <si>
-    <t>0.1559,0.0346,0.8399,0.0270</t>
-  </si>
-  <si>
-    <t>0.6300,0.0095,0.3494,0.0556</t>
-  </si>
-  <si>
-    <t>0.7641,0.0037,0.2775,0.0212</t>
-  </si>
-  <si>
-    <t>0.7995,0.0058,0.0192,0.1997</t>
-  </si>
-  <si>
-    <t>0.9884,0.0125,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9811,0.0278,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0021,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9652,0.0334,0.0067,0.0014</t>
-  </si>
-  <si>
-    <t>0.9764,0.0120,0.0010,0.0026</t>
-  </si>
-  <si>
-    <t>0.9965,0.0020,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9958,0.0019,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9863,0.0039,0.0008,0.0022</t>
-  </si>
-  <si>
-    <t>0.0128,0.0614,0.9508,0.0009</t>
-  </si>
-  <si>
-    <t>0.0102,0.0293,0.9753,0.0024</t>
-  </si>
-  <si>
-    <t>0.0096,0.0277,0.9695,0.0059</t>
-  </si>
-  <si>
-    <t>0.3157,0.0812,0.5607,0.0033</t>
-  </si>
-  <si>
-    <t>0.0017,0.0138,0.9921,0.0013</t>
-  </si>
-  <si>
-    <t>0.1116,0.0092,0.8688,0.0502</t>
-  </si>
-  <si>
-    <t>0.1822,0.0438,0.8221,0.0109</t>
-  </si>
-  <si>
-    <t>0.0033,0.0012,0.9829,0.0296</t>
-  </si>
-  <si>
-    <t>0.9486,0.0019,0.0041,0.0557</t>
-  </si>
-  <si>
-    <t>0.0199,0.1940,0.0087,0.9695</t>
-  </si>
-  <si>
-    <t>0.0179,0.0011,0.0070,0.9868</t>
-  </si>
-  <si>
-    <t>0.0024,0.0000,0.0005,0.9987</t>
-  </si>
-  <si>
-    <t>0.0098,0.0039,0.0005,0.9961</t>
-  </si>
-  <si>
-    <t>0.8831,0.0111,0.0106,0.0962</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.8707,0.0988,0.0203,0.0102</t>
+  </si>
+  <si>
+    <t>0.1276,0.0049,0.0035,0.9560</t>
+  </si>
+  <si>
+    <t>0.8896,0.0341,0.0183,0.0467</t>
+  </si>
+  <si>
+    <t>0.0699,0.0060,0.0007,0.9787</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0022,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9872,0.0088,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9966,0.0013,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9956,0.0038,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9931,0.0088,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0009,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0010,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.6274,0.1849,0.1428,0.0465</t>
+  </si>
+  <si>
+    <t>0.1294,0.0278,0.8945,0.0022</t>
+  </si>
+  <si>
+    <t>0.1478,0.2720,0.6071,0.0059</t>
+  </si>
+  <si>
+    <t>0.3782,0.1023,0.5197,0.0043</t>
+  </si>
+  <si>
+    <t>0.6862,0.1415,0.2406,0.0064</t>
+  </si>
+  <si>
+    <t>0.0187,0.9770,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.0170,0.9817,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.5436,0.5365,0.0247,0.0027</t>
+  </si>
+  <si>
+    <t>0.2473,0.8475,0.0069,0.0003</t>
+  </si>
+  <si>
+    <t>0.0798,0.9349,0.0098,0.0005</t>
+  </si>
+  <si>
+    <t>0.4665,0.0017,0.2716,0.1286</t>
+  </si>
+  <si>
+    <t>0.6371,0.0322,0.2105,0.1691</t>
+  </si>
+  <si>
+    <t>0.2033,0.0200,0.8275,0.0157</t>
+  </si>
+  <si>
+    <t>0.0918,0.0229,0.8978,0.0268</t>
+  </si>
+  <si>
+    <t>0.0206,0.0064,0.9808,0.0028</t>
+  </si>
+  <si>
+    <t>0.2731,0.0137,0.8181,0.0084</t>
+  </si>
+  <si>
+    <t>0.0121,0.0043,0.9793,0.0068</t>
+  </si>
+  <si>
+    <t>0.3135,0.7848,0.0095,0.0008</t>
+  </si>
+  <si>
+    <t>0.5383,0.4134,0.1420,0.0060</t>
+  </si>
+  <si>
+    <t>0.0015,0.1064,0.9846,0.0017</t>
+  </si>
+  <si>
+    <t>0.0180,0.7728,0.4258,0.0001</t>
+  </si>
+  <si>
+    <t>0.7857,0.1990,0.0476,0.0053</t>
+  </si>
+  <si>
+    <t>0.5726,0.4731,0.0349,0.0058</t>
+  </si>
+  <si>
+    <t>0.6986,0.4677,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.0885,0.8372,0.2669,0.0046</t>
+  </si>
+  <si>
+    <t>0.0174,0.8691,0.1892,0.0222</t>
+  </si>
+  <si>
+    <t>0.0225,0.0387,0.9314,0.0148</t>
+  </si>
+  <si>
+    <t>0.0310,0.3666,0.8099,0.0305</t>
+  </si>
+  <si>
+    <t>0.0449,0.0509,0.8880,0.0298</t>
+  </si>
+  <si>
+    <t>0.0515,0.1111,0.8656,0.0073</t>
+  </si>
+  <si>
+    <t>0.0115,0.9546,0.0579,0.0005</t>
+  </si>
+  <si>
+    <t>0.0369,0.2560,0.8026,0.0069</t>
+  </si>
+  <si>
+    <t>0.1017,0.4582,0.0837,0.8231</t>
+  </si>
+  <si>
+    <t>0.0181,0.9548,0.0175,0.0157</t>
+  </si>
+  <si>
+    <t>0.0146,0.9392,0.1908,0.0021</t>
+  </si>
+  <si>
+    <t>0.0009,0.9923,0.0145,0.0016</t>
+  </si>
+  <si>
+    <t>0.0477,0.1093,0.8734,0.0331</t>
+  </si>
+  <si>
+    <t>0.0056,0.0707,0.9853,0.0007</t>
+  </si>
+  <si>
+    <t>0.0476,0.0019,0.9724,0.0010</t>
+  </si>
+  <si>
+    <t>0.0395,0.0063,0.9619,0.0044</t>
+  </si>
+  <si>
+    <t>0.0005,0.0163,0.9942,0.0014</t>
+  </si>
+  <si>
+    <t>0.0029,0.0297,0.9847,0.0006</t>
+  </si>
+  <si>
+    <t>0.9409,0.0928,0.0038,0.0009</t>
+  </si>
+  <si>
+    <t>0.9767,0.0068,0.0072,0.0036</t>
+  </si>
+  <si>
+    <t>0.9818,0.0195,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.0078,0.4115,0.9468,0.0016</t>
+  </si>
+  <si>
+    <t>0.9814,0.0112,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9960,0.0010,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9877,0.0113,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.7004,0.9651,0.0003</t>
+  </si>
+  <si>
+    <t>0.0066,0.1837,0.9730,0.0016</t>
+  </si>
+  <si>
+    <t>0.0095,0.1081,0.9716,0.0037</t>
+  </si>
+  <si>
+    <t>0.0005,0.8477,0.9700,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0104,0.9891,0.0041</t>
+  </si>
+  <si>
+    <t>0.0276,0.9223,0.1349,0.0023</t>
+  </si>
+  <si>
+    <t>0.0710,0.9426,0.0045,0.0010</t>
+  </si>
+  <si>
+    <t>0.8473,0.0339,0.1866,0.0026</t>
+  </si>
+  <si>
+    <t>0.6635,0.1186,0.3302,0.0063</t>
+  </si>
+  <si>
+    <t>0.0009,0.0153,0.9943,0.0011</t>
+  </si>
+  <si>
+    <t>0.0020,0.9372,0.7945,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.9823,0.2670,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9812,0.2023,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.8687,0.9235,0.0010</t>
+  </si>
+  <si>
+    <t>0.0418,0.0010,0.0877,0.9265</t>
+  </si>
+  <si>
+    <t>0.0012,0.0040,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0140,0.0033,0.0041,0.9904</t>
+  </si>
+  <si>
+    <t>0.0334,0.0008,0.0146,0.9702</t>
+  </si>
+  <si>
+    <t>0.0104,0.0002,0.0039,0.9928</t>
+  </si>
+  <si>
+    <t>0.0217,0.0551,0.0065,0.9802</t>
+  </si>
+  <si>
+    <t>0.0010,0.9654,0.7644,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.6358,0.9559,0.0002</t>
+  </si>
+  <si>
+    <t>0.0249,0.7646,0.4455,0.0051</t>
+  </si>
+  <si>
+    <t>0.0070,0.3561,0.9262,0.0010</t>
+  </si>
+  <si>
+    <t>0.0007,0.9695,0.6574,0.0000</t>
+  </si>
+  <si>
+    <t>0.0065,0.9553,0.1346,0.0002</t>
+  </si>
+  <si>
+    <t>0.9782,0.0253,0.0041,0.0003</t>
+  </si>
+  <si>
+    <t>0.9893,0.0136,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9847,0.0190,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9875,0.0096,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9939,0.0084,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9860,0.0167,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9910,0.0048,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9927,0.0062,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0050,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0018,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9931,0.0020,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9971,0.0020,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0015,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9949,0.0006,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.0469,0.0030,0.9721,0.0033</t>
+  </si>
+  <si>
+    <t>0.0619,0.0035,0.9556,0.0071</t>
+  </si>
+  <si>
+    <t>0.8960,0.0053,0.0900,0.0123</t>
+  </si>
+  <si>
+    <t>0.2548,0.0222,0.7859,0.0157</t>
+  </si>
+  <si>
+    <t>0.0703,0.9270,0.0186,0.0005</t>
+  </si>
+  <si>
+    <t>0.0521,0.9522,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.1693,0.8543,0.0027,0.0031</t>
+  </si>
+  <si>
+    <t>0.1639,0.9068,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.0204,0.9741,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.0370,0.9370,0.0322,0.0011</t>
+  </si>
+  <si>
+    <t>0.2296,0.8565,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0679,0.8947,0.0208,0.0678</t>
+  </si>
+  <si>
+    <t>0.1165,0.0139,0.9168,0.0075</t>
+  </si>
+  <si>
+    <t>0.2528,0.0531,0.7471,0.0240</t>
+  </si>
+  <si>
+    <t>0.4205,0.2059,0.4897,0.0243</t>
+  </si>
+  <si>
+    <t>0.5197,0.1114,0.1568,0.3365</t>
+  </si>
+  <si>
+    <t>0.0083,0.9714,0.0420,0.0115</t>
+  </si>
+  <si>
+    <t>0.0051,0.9622,0.0300,0.0434</t>
+  </si>
+  <si>
+    <t>0.0811,0.8809,0.0196,0.0203</t>
+  </si>
+  <si>
+    <t>0.0014,0.7462,0.9632,0.0014</t>
+  </si>
+  <si>
+    <t>0.0247,0.9658,0.0553,0.0001</t>
+  </si>
+  <si>
+    <t>0.6899,0.3381,0.0324,0.0016</t>
+  </si>
+  <si>
+    <t>0.2658,0.8169,0.0087,0.0003</t>
+  </si>
+  <si>
+    <t>0.9939,0.0036,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9870,0.0025,0.0006,0.0029</t>
+  </si>
+  <si>
+    <t>0.9951,0.0025,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9802,0.0061,0.0031,0.0030</t>
+  </si>
+  <si>
+    <t>0.9955,0.0022,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9707,0.0256,0.0103,0.0004</t>
+  </si>
+  <si>
+    <t>0.9912,0.0028,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9957,0.0018,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.7183,0.8433,0.0015</t>
+  </si>
+  <si>
+    <t>0.0058,0.6618,0.8539,0.0009</t>
+  </si>
+  <si>
+    <t>0.0073,0.0378,0.9718,0.0064</t>
+  </si>
+  <si>
+    <t>0.0107,0.2908,0.9129,0.0049</t>
+  </si>
+  <si>
+    <t>0.4569,0.5124,0.0478,0.0355</t>
+  </si>
+  <si>
+    <t>0.7128,0.1019,0.1856,0.0280</t>
+  </si>
+  <si>
+    <t>0.7296,0.0044,0.4716,0.0087</t>
+  </si>
+  <si>
+    <t>0.3560,0.4028,0.2999,0.0325</t>
+  </si>
+  <si>
+    <t>0.0096,0.0113,0.0023,0.9934</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0010,0.9997</t>
+  </si>
+  <si>
+    <t>0.0020,0.0670,0.0015,0.9961</t>
+  </si>
+  <si>
+    <t>0.0193,0.0014,0.0051,0.9877</t>
+  </si>
+  <si>
+    <t>0.0113,0.5388,0.9264,0.0026</t>
+  </si>
+  <si>
+    <t>0.9728,0.0295,0.0031,0.0007</t>
+  </si>
+  <si>
+    <t>0.2432,0.8228,0.0052,0.0035</t>
+  </si>
+  <si>
+    <t>0.9859,0.0061,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.4536,0.6941,0.0050,0.0013</t>
+  </si>
+  <si>
+    <t>0.9257,0.0864,0.0041,0.0022</t>
+  </si>
+  <si>
+    <t>0.5681,0.0066,0.0770,0.3478</t>
+  </si>
+  <si>
+    <t>0.9770,0.0108,0.0023,0.0026</t>
+  </si>
+  <si>
+    <t>0.0064,0.1503,0.9451,0.0123</t>
+  </si>
+  <si>
+    <t>0.9266,0.0009,0.0119,0.0359</t>
+  </si>
+  <si>
+    <t>0.8512,0.0285,0.0524,0.0648</t>
+  </si>
+  <si>
+    <t>0.2220,0.8256,0.0147,0.0054</t>
+  </si>
+  <si>
+    <t>0.7237,0.3033,0.0194,0.0136</t>
+  </si>
+  <si>
+    <t>0.8315,0.1576,0.0403,0.0014</t>
+  </si>
+  <si>
+    <t>0.2029,0.8029,0.0128,0.0094</t>
+  </si>
+  <si>
+    <t>0.5787,0.4918,0.0285,0.0012</t>
+  </si>
+  <si>
+    <t>0.4692,0.5343,0.0462,0.0468</t>
+  </si>
+  <si>
+    <t>0.9863,0.0022,0.0010,0.0035</t>
+  </si>
+  <si>
+    <t>0.9745,0.0057,0.0008,0.0064</t>
+  </si>
+  <si>
+    <t>0.9928,0.0031,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0015,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9913,0.0022,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9914,0.0028,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9840,0.0115,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9945,0.0016,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.1878,0.8626,0.0058,0.0020</t>
+  </si>
+  <si>
+    <t>0.4327,0.7437,0.0023,0.0005</t>
+  </si>
+  <si>
+    <t>0.1007,0.8861,0.0363,0.0004</t>
+  </si>
+  <si>
+    <t>0.1644,0.0896,0.8254,0.0033</t>
+  </si>
+  <si>
+    <t>0.9302,0.0760,0.0056,0.0029</t>
+  </si>
+  <si>
+    <t>0.9383,0.0511,0.0145,0.0022</t>
+  </si>
+  <si>
+    <t>0.8868,0.1660,0.0067,0.0022</t>
+  </si>
+  <si>
+    <t>0.9748,0.0116,0.0051,0.0018</t>
+  </si>
+  <si>
+    <t>0.0043,0.0190,0.9907,0.0008</t>
+  </si>
+  <si>
+    <t>0.9762,0.0123,0.0013,0.0026</t>
+  </si>
+  <si>
+    <t>0.0366,0.0172,0.9674,0.0013</t>
+  </si>
+  <si>
+    <t>0.0079,0.3968,0.9308,0.0031</t>
+  </si>
+  <si>
+    <t>0.0092,0.0016,0.9927,0.0011</t>
+  </si>
+  <si>
+    <t>0.0286,0.0661,0.9444,0.0065</t>
+  </si>
+  <si>
+    <t>0.0403,0.0308,0.9514,0.0018</t>
+  </si>
+  <si>
+    <t>0.0046,0.0017,0.9954,0.0001</t>
+  </si>
+  <si>
+    <t>0.0051,0.0293,0.9862,0.0002</t>
+  </si>
+  <si>
+    <t>0.0490,0.0441,0.9302,0.0018</t>
+  </si>
+  <si>
+    <t>0.1445,0.0514,0.8364,0.0026</t>
+  </si>
+  <si>
+    <t>0.4046,0.0290,0.7146,0.0097</t>
+  </si>
+  <si>
+    <t>0.2110,0.4838,0.2953,0.0031</t>
+  </si>
+  <si>
+    <t>0.0584,0.3871,0.6058,0.0021</t>
+  </si>
+  <si>
+    <t>0.5356,0.1841,0.2916,0.0055</t>
+  </si>
+  <si>
+    <t>0.3364,0.3331,0.3060,0.0112</t>
+  </si>
+  <si>
+    <t>0.1814,0.0535,0.7626,0.0040</t>
+  </si>
+  <si>
+    <t>0.8866,0.1863,0.0046,0.0007</t>
+  </si>
+  <si>
+    <t>0.6774,0.4781,0.0056,0.0004</t>
+  </si>
+  <si>
+    <t>0.8819,0.1180,0.0290,0.0005</t>
+  </si>
+  <si>
+    <t>0.9816,0.0225,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.6436,0.5340,0.0054,0.0008</t>
+  </si>
+  <si>
+    <t>0.4795,0.3007,0.1794,0.0049</t>
+  </si>
+  <si>
+    <t>0.8182,0.0148,0.1829,0.0197</t>
+  </si>
+  <si>
+    <t>0.5608,0.0873,0.0129,0.2810</t>
+  </si>
+  <si>
+    <t>0.6925,0.0229,0.3864,0.0165</t>
+  </si>
+  <si>
+    <t>0.7407,0.0104,0.3341,0.0159</t>
+  </si>
+  <si>
+    <t>0.0452,0.0067,0.9514,0.0234</t>
+  </si>
+  <si>
+    <t>0.1189,0.4846,0.5607,0.0301</t>
+  </si>
+  <si>
+    <t>0.0642,0.1036,0.8385,0.0074</t>
+  </si>
+  <si>
+    <t>0.0783,0.0641,0.8749,0.0127</t>
+  </si>
+  <si>
+    <t>0.0102,0.6517,0.8269,0.0035</t>
+  </si>
+  <si>
+    <t>0.9773,0.0270,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9912,0.0114,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9780,0.0235,0.0021,0.0006</t>
+  </si>
+  <si>
+    <t>0.9782,0.0118,0.0026,0.0025</t>
+  </si>
+  <si>
+    <t>0.9880,0.0086,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9932,0.0060,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9849,0.0095,0.0018,0.0014</t>
+  </si>
+  <si>
+    <t>0.9890,0.0082,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.0483,0.0177,0.9553,0.0073</t>
+  </si>
+  <si>
+    <t>0.1159,0.4262,0.5607,0.0058</t>
+  </si>
+  <si>
+    <t>0.6572,0.1289,0.2707,0.0178</t>
+  </si>
+  <si>
+    <t>0.0084,0.2025,0.9521,0.0042</t>
+  </si>
+  <si>
+    <t>0.0024,0.0122,0.9923,0.0012</t>
+  </si>
+  <si>
+    <t>0.0820,0.1362,0.7463,0.0068</t>
+  </si>
+  <si>
+    <t>0.0026,0.0076,0.9928,0.0016</t>
+  </si>
+  <si>
+    <t>0.0133,0.0899,0.9339,0.0071</t>
+  </si>
+  <si>
+    <t>0.0046,0.0448,0.9793,0.0018</t>
+  </si>
+  <si>
+    <t>0.0118,0.0739,0.9462,0.0099</t>
+  </si>
+  <si>
+    <t>0.1898,0.0516,0.8148,0.0034</t>
+  </si>
+  <si>
+    <t>0.4999,0.0191,0.6370,0.0199</t>
+  </si>
+  <si>
+    <t>0.3951,0.0258,0.7262,0.0080</t>
+  </si>
+  <si>
+    <t>0.6665,0.0101,0.4004,0.0267</t>
+  </si>
+  <si>
+    <t>0.9931,0.0060,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9932,0.0040,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0019,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9613,0.0579,0.0051,0.0004</t>
+  </si>
+  <si>
+    <t>0.9928,0.0010,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9926,0.0086,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9924,0.0051,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0159,0.1575,0.8860,0.0013</t>
+  </si>
+  <si>
+    <t>0.0090,0.0698,0.9690,0.0026</t>
+  </si>
+  <si>
+    <t>0.0118,0.0212,0.9672,0.0065</t>
+  </si>
+  <si>
+    <t>0.0364,0.1955,0.7725,0.0075</t>
+  </si>
+  <si>
+    <t>0.0046,0.0034,0.9906,0.0016</t>
+  </si>
+  <si>
+    <t>0.1282,0.0198,0.8487,0.0401</t>
+  </si>
+  <si>
+    <t>0.0453,0.0621,0.9132,0.0087</t>
+  </si>
+  <si>
+    <t>0.0109,0.0086,0.9659,0.0179</t>
+  </si>
+  <si>
+    <t>0.8001,0.0013,0.0040,0.2808</t>
+  </si>
+  <si>
+    <t>0.0823,0.0151,0.0043,0.9605</t>
+  </si>
+  <si>
+    <t>0.1584,0.0032,0.0118,0.9135</t>
+  </si>
+  <si>
+    <t>0.0012,0.0063,0.0006,0.9988</t>
+  </si>
+  <si>
+    <t>0.0003,0.0048,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.8262,0.0969,0.0514,0.0388</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2225,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,10 +2421,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2928,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2967,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3163,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,10 +3891,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3919,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4059,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,10 +4227,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4622,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4692,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4759,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4818,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4857,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
